--- a/光伏配储项目/电价数据/2026/万绿湖站.xlsx
+++ b/光伏配储项目/电价数据/2026/万绿湖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48692</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75587</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54561</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.55863</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48778</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.48038</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47406</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.16571</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23858</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.02781</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01753</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.08112999999999999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.04865999999999999</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.16202</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.10966</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.00391</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5347499999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73388</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.1184</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.16919</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66112</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8608899999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19218</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.46773</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.32233</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.27758</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.53652</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67872</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.72903</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.09963</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.96304</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89112</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8002400000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7611</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51506</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42744</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71674</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8881599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94059</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5091100000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50926</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47277</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.13794</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.99617</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.0598</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.15384</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.58411</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.01506</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.69577</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.6286499999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.01302</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.13656</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.81238</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26765</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5902200000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5965499999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74585</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.75729</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.1609</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24751</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13623</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83899</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20481</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10579</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25641</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02338</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09009</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65058</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98299</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91318</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95858</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78528</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8935700000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.74088</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77709</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.73199</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76379</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33492</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49277</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44632</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.1027</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.03325</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22499</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.10769</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78303</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.42602</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.51666</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.44795</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28419</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62083</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64251</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46583</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.55426</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6138400000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48415</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61719</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.57731</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55788</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7210800000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.52179</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55769</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34232</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.07773000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.16264</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.07160999999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5667300000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.17098</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.15844</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62239</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44811</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48886</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43946</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55752</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49239</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50425</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3212</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.12477</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.08815000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.16449</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.10756</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13415</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.12073</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.03052</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.18589</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.06102</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.02232</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.36984</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.84057</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.52178</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5339400000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.58804</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10219</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04321</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04586999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15813</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03086</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34642</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32294</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78546</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86909</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56865</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33082</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5403600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39986</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6609700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62524</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.80852</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88373</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.49005</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.65963</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.49475</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.78754</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87325</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.50903</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.88597</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8251499999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59126</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.47436</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5327799999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.47788</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37022</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9346</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.52325</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54455</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.46112</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6038300000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.22854</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.09797</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20062</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.45747</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.45892</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.76701</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48164</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19876</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72739</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8192200000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67853</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.78391</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.5841499999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52498</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49251</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47378</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.60446</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.54104</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43337</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.46255</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.50382</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.46834</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6236799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.53747</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25153</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01576</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26414</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.64554</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.54111</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.00611</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.54722</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.50697</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36589</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.44129</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50482</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5325299999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.43532</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5180399999999999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21573</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10309</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08961</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09612000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10623</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23198</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13515</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.06006</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.03714</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.07006999999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.06374</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16518</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.53618</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.53606</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.52239</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.51866</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5250900000000001</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.38691</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.66752</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.48892</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44202</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.53523</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26738</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.22891</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21757</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.17754</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.89263</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.51203</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39157</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.62158</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.62944</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.14204</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67879</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51062</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.4626</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5738799999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.05794</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47847</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46353</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71715</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.02729</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.71169</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52678</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.64113</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.41744</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5089399999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42702</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.43817</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.45693</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36677</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.57475</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42517</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.48522</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6731699999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.05111</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5170399999999999</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.53847</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3713</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11071</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.21607</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.18763</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.13313</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.20194</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.23342</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.23518</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.16036</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22084</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.45939</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67703</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63463</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6510900000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.63367</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84477</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.60878</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.16213</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.6484500000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.59387</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38719</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5822999999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.71428</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.88683</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47297</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.46473</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47281</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44407</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43378</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.45644</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46102</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5491</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.53808</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.61294</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5321900000000001</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.60266</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.52844</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.46507</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.90974</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.45938</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.46674</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.50201</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.58888</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.52934</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6920299999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.92777</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.14654</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.26108</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.90865</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.07654</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.89847</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.68277</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.11799</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78679</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6402899999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68957</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.55257</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.58128</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.57885</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.56762</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.55944</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.68277</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.51215</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.53599</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45163</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44158</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46203</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.43729</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.08314</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.17228</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.56321</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.00594</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.11349</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.48436</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.46089</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5164099999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.48329</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.49374</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.50976</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.48978</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.49831</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.47292</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.5157999999999999</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.45707</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.61361</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.48903</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.45735</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.60153</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.45699</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.54211</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.43318</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.5404099999999999</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.48267</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.5400199999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.18556</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21455</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23139</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06825000000000001</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.09684999999999999</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.11616</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22632</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.46526</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.48858</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49186</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.45188</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.41791</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.49853</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.48822</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.49882</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.5020899999999999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02262</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02945</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03904999999999999</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03644</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01528</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20529</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.49525</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40326</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.14986</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9853999999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.48455</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.84009</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.51524</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.47079</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.6091</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.6306900000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.54399</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.62078</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.56957</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6241</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.59182</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.60166</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.64206</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.52416</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.56755</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.50906</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.43872</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.36197</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.90791</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.02294</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02324</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.55496</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.02589</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.02143</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04118</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.02481</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02553</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.02481</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.12249</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.10978</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.0303</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.11944</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86114</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.85939</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86354</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96038</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.11142</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.11541</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.10641</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41752</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.87042</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.40299</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.81737</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51685</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.61078</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.50959</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.51697</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.5931900000000001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.49447</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6037899999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.65655</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.19103</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.009529999999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.07590000000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.03189</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.02728</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.00898</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.21352</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42661</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.61602</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.20535</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.60138</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.52907</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.66092</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.39858</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.50808</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5380499999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8354299999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.9940800000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.81602</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.23651</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.75735</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.58356</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.9524</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82997</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5710599999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55559</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6449400000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81749</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.90911</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.78969</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.60036</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6027899999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.53103</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.39923</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5244800000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66622</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6334299999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.76876</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54062</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.76542</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46341</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.93262</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.9979600000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40344</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.5855399999999999</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.43946</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17891</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27286</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17527</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21088</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09656000000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.17528</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00193</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05893</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26528</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11292</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23328</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18445</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20903</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5402400000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.51407</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43623</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41515</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.23617</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.09511</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.23547</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23167</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02792</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.07524</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38692</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14634</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.01059</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.02839</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.01409</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0005899999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13714</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18096</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.009339999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.05923</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20254</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14746</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25832</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40673</v>
       </c>
     </row>
   </sheetData>
